--- a/PythonScripts/PILSNER_Kereskedelmi_Betéti_Társaság_Beszamolo_Elemzes.xlsx
+++ b/PythonScripts/PILSNER_Kereskedelmi_Betéti_Társaság_Beszamolo_Elemzes.xlsx
@@ -1348,34 +1348,34 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>82</v>
+        <v>202</v>
       </c>
       <c r="C26" t="n">
-        <v>83</v>
+        <v>203</v>
       </c>
       <c r="D26" t="n">
-        <v>84</v>
+        <v>204</v>
       </c>
       <c r="E26" t="n">
-        <v>85</v>
+        <v>205</v>
       </c>
       <c r="F26" t="n">
-        <v>86</v>
+        <v>206</v>
       </c>
       <c r="G26" t="n">
-        <v>87</v>
+        <v>207</v>
       </c>
       <c r="H26" t="n">
-        <v>88</v>
+        <v>208</v>
       </c>
       <c r="I26" t="n">
-        <v>89</v>
+        <v>209</v>
       </c>
       <c r="J26" t="n">
-        <v>90</v>
+        <v>210</v>
       </c>
       <c r="K26" t="n">
-        <v>91</v>
+        <v>211</v>
       </c>
     </row>
     <row r="27">
@@ -5791,13 +5791,13 @@
         <v>0</v>
       </c>
       <c r="C146" t="n">
-        <v>2027</v>
+        <v>0</v>
       </c>
       <c r="D146" t="n">
         <v>0</v>
       </c>
       <c r="E146" t="n">
-        <v>915</v>
+        <v>0</v>
       </c>
       <c r="F146" t="n">
         <v>0</v>
@@ -6269,16 +6269,16 @@
         </is>
       </c>
       <c r="B159" t="n">
-        <v>7251</v>
+        <v>0</v>
       </c>
       <c r="C159" t="n">
         <v>0</v>
       </c>
       <c r="D159" t="n">
-        <v>1724</v>
+        <v>0</v>
       </c>
       <c r="E159" t="n">
-        <v>1620</v>
+        <v>0</v>
       </c>
       <c r="F159" t="n">
         <v>0</v>
@@ -6290,13 +6290,13 @@
         <v>0</v>
       </c>
       <c r="I159" t="n">
-        <v>257</v>
+        <v>0</v>
       </c>
       <c r="J159" t="n">
-        <v>1368</v>
+        <v>0</v>
       </c>
       <c r="K159" t="n">
-        <v>978</v>
+        <v>0</v>
       </c>
     </row>
     <row r="160">
@@ -6364,7 +6364,7 @@
         <v>0</v>
       </c>
       <c r="I161" t="n">
-        <v>265</v>
+        <v>0</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -6565,34 +6565,34 @@
         </is>
       </c>
       <c r="B167" t="n">
-        <v>297</v>
+        <v>0</v>
       </c>
       <c r="C167" t="n">
-        <v>125</v>
+        <v>0</v>
       </c>
       <c r="D167" t="n">
-        <v>271</v>
+        <v>0</v>
       </c>
       <c r="E167" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F167" t="n">
-        <v>260</v>
+        <v>0</v>
       </c>
       <c r="G167" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H167" t="n">
-        <v>1991</v>
+        <v>0</v>
       </c>
       <c r="I167" t="n">
-        <v>11210</v>
+        <v>0</v>
       </c>
       <c r="J167" t="n">
-        <v>7419</v>
+        <v>0</v>
       </c>
       <c r="K167" t="n">
-        <v>10228</v>
+        <v>0</v>
       </c>
     </row>
     <row r="168">
@@ -6639,7 +6639,7 @@
         </is>
       </c>
       <c r="B169" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C169" t="n">
         <v>0</v>
@@ -6916,13 +6916,13 @@
         <v>0</v>
       </c>
       <c r="H176" t="n">
-        <v>887</v>
+        <v>0</v>
       </c>
       <c r="I176" t="n">
         <v>0</v>
       </c>
       <c r="J176" t="n">
-        <v>1223</v>
+        <v>0</v>
       </c>
       <c r="K176" t="n">
         <v>0</v>
@@ -7030,7 +7030,7 @@
         <v>0</v>
       </c>
       <c r="I179" t="n">
-        <v>9481</v>
+        <v>0</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -7304,7 +7304,9 @@
           <t>MUTATO: Vagyon változása (%)</t>
         </is>
       </c>
-      <c r="B187" t="inlineStr"/>
+      <c r="B187" t="n">
+        <v>0</v>
+      </c>
       <c r="C187" t="n">
         <v>10.16514065126519</v>
       </c>
